--- a/yuyang_care_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/yuyang_care_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -1139,7 +1139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1150,6 +1150,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1191,6 +1192,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>时间</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>操作人</t>
         </is>
       </c>
     </row>
